--- a/作成中事業計画書/20261001【更新版】★20260930スケジュール（トンボ飲料様）.xlsx
+++ b/作成中事業計画書/20261001【更新版】★20260930スケジュール（トンボ飲料様）.xlsx
@@ -364,7 +364,7 @@
 　付加価値創出</t>
   </si>
   <si>
-    <t>導入後も統括責任者の下で月次進捗会議を続け、創出時間・遅番の派遣依存などのKPIを確認し、未達があれば配置と手順を見直す。
+    <t>導入後も統括責任者の下で月次進捗会議を続け、3章のKPI（創出時間、カバー出勤件数、習熟者数、遅番担当日数、工程内検査件数、ODM試作件数、マニュアル整備件数）を確認し、未達があれば配置と手順を見直す。
 創出した時間は3段階で人に再配置する。
 段階1（基準年度〜1年目）は中番パートの多能工化教育とマニュアル化、段階2（1〜2年目）は多能工化したパートによる遅番オペレーター業務の担当である。
 段階3（2〜3年目）は、日勤に戻った社員による品質管理・提案型ODM・技術継承と、Eライン横展開の準備である。
